--- a/bancos/manual/desc_grupos_de_despesa.xlsx
+++ b/bancos/manual/desc_grupos_de_despesa.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29301"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="S:\2.Programação e Normas\2023\PPAG 2023 e LOA 2023\Tabelas de Apoio - geração dos volumes 2023\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\x1569275\CAMG\Splor Geral - @dcppn\00- DCPPN 2027\PPAG e LOA 2027\Dados para Volumes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_EE1514BD93A0E587D9DD422898642CD98D28E8D4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="15345" windowHeight="3645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="15345" windowHeight="3645"/>
   </bookViews>
   <sheets>
     <sheet name="Plan1" sheetId="1" r:id="rId1"/>
@@ -18,7 +17,7 @@
   <definedNames>
     <definedName name="LOCAL_MYSQL_DATE_FORMAT" hidden="1">REPT(LOCAL_YEAR_FORMAT,4)&amp;LOCAL_DATE_SEPARATOR&amp;REPT(LOCAL_MONTH_FORMAT,2)&amp;LOCAL_DATE_SEPARATOR&amp;REPT(LOCAL_DAY_FORMAT,2)&amp;" "&amp;REPT(LOCAL_HOUR_FORMAT,2)&amp;LOCAL_TIME_SEPARATOR&amp;REPT(LOCAL_MINUTE_FORMAT,2)&amp;LOCAL_TIME_SEPARATOR&amp;REPT(LOCAL_SECOND_FORMAT,2)</definedName>
   </definedNames>
-  <calcPr calcId="191028"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -95,8 +94,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -413,16 +412,16 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="27.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="99.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -433,7 +432,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -444,7 +443,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -455,7 +454,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -466,7 +465,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -477,7 +476,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -488,7 +487,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
@@ -499,7 +498,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>9</v>
       </c>
@@ -516,26 +515,17 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="b91e7f20-fe0a-487d-91a9-605ac1c64acf" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="6f4338ef-addb-4c87-aefe-1895241b335f">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <SharedWithUsers xmlns="b91e7f20-fe0a-487d-91a9-605ac1c64acf">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </SharedWithUsers>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100B08D58FADB61F04EBBB4F355C06EFBED" ma:contentTypeVersion="19" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="7797dc5feb179b4da55a9ebddd321181">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="6f4338ef-addb-4c87-aefe-1895241b335f" xmlns:ns3="b91e7f20-fe0a-487d-91a9-605ac1c64acf" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="90078f443198b6d5c0fd169535a443b9" ns2:_="" ns3:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100B08D58FADB61F04EBBB4F355C06EFBED" ma:contentTypeVersion="19" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="b1e0f6055e0e9a4b9e75d6c71ee7de91">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="6f4338ef-addb-4c87-aefe-1895241b335f" xmlns:ns3="b91e7f20-fe0a-487d-91a9-605ac1c64acf" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="b43930f3490e4d4da1ab3f8da7df6f51" ns2:_="" ns3:_="">
     <xsd:import namespace="6f4338ef-addb-4c87-aefe-1895241b335f"/>
     <xsd:import namespace="b91e7f20-fe0a-487d-91a9-605ac1c64acf"/>
     <xsd:element name="properties">
@@ -795,22 +785,63 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="b91e7f20-fe0a-487d-91a9-605ac1c64acf" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="6f4338ef-addb-4c87-aefe-1895241b335f">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <SharedWithUsers xmlns="b91e7f20-fe0a-487d-91a9-605ac1c64acf">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </SharedWithUsers>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5235E97D-0D6E-428F-ADE0-B39700FDC0DD}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FE650D08-EC1B-4F30-B6C6-7AAA03CE30AC}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B842B0B9-EE3F-439C-AEFC-C68B7CCE633D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{88764D5C-BB36-4FB8-8B83-EC3125FCC87A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="6f4338ef-addb-4c87-aefe-1895241b335f"/>
+    <ds:schemaRef ds:uri="b91e7f20-fe0a-487d-91a9-605ac1c64acf"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FE650D08-EC1B-4F30-B6C6-7AAA03CE30AC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5235E97D-0D6E-428F-ADE0-B39700FDC0DD}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="b91e7f20-fe0a-487d-91a9-605ac1c64acf"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="6f4338ef-addb-4c87-aefe-1895241b335f"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>